--- a/admin/public/imports/product/zh.xlsx
+++ b/admin/public/imports/product/zh.xlsx
@@ -1,26 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac-020/Desktop/jjjshop-saas/jjj_food_chain/public/imports/product/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B53F7A15-DDE6-D64A-933A-4264B0BC34C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8300" yWindow="2160" windowWidth="20960" windowHeight="9720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="23960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>*商品名称</t>
   </si>
@@ -30,7 +37,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">*所属分类
@@ -41,7 +48,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>（二级分类请以/分隔）</t>
@@ -53,7 +60,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">*库存计算方式
@@ -64,7 +71,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>（下单减库存=1/付款减库存=2）</t>
@@ -85,7 +92,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">*库存数量
@@ -96,7 +103,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>（最大库存：99999999）</t>
@@ -114,7 +121,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">*商品状态
@@ -125,7 +132,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>（上架=1/下架=0）</t>
@@ -143,7 +150,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">*显示
@@ -154,7 +161,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>（可多选，是否显示到：收银机=1/平板=2/厨显=3/点餐助手=4/扫码点餐=5）</t>
@@ -169,7 +176,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">限购数量
@@ -180,194 +187,758 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>（0为不限购）</t>
     </r>
   </si>
   <si>
-    <t>（例，导入时请删除此行）
-English:Caramel pudding
-ภาษาไทย:พุดดิ้งคาราเมล
-简体中文:焦糖布丁
-繁體中文:焦糖布丁
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>会员折扣</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（开启</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>关闭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">English:Caramel pudding
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ภาษาไทย</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <charset val="134"/>
+      </rPr>
+      <t>พุดดิ้งคาราเมล</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>简体中文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>焦糖布丁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>繁體中文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>焦糖布丁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
 Türkçe:crème brûlée
 မြန်မာဘာသာ:ရွှင်ဆူမန်
-日本語:クレームブリュレ
-한국어:크림 브륄레</t>
-  </si>
-  <si>
-    <t>甜品/港式甜品</t>
-  </si>
-  <si>
-    <t>份</t>
-  </si>
-  <si>
-    <t>酒水类</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>会员折扣</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>日本語</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="冬青黑体简体中文"/>
+        <charset val="134"/>
+      </rPr>
+      <t>クレームブリュレ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
 </t>
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（开启</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>=1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Apple SD Gothic Neo"/>
+        <charset val="134"/>
+      </rPr>
+      <t>한국어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Apple SD Gothic Neo"/>
+        <charset val="134"/>
+      </rPr>
+      <t>크림</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Apple SD Gothic Neo"/>
+        <charset val="134"/>
+      </rPr>
+      <t>브륄레</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>甜点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>/</t>
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>关闭</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>=0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>非常甜</t>
+    </r>
+  </si>
+  <si>
+    <t>份</t>
+  </si>
+  <si>
+    <t>小</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="31">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <name val="宋体-简"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="冬青黑体简体中文"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Apple SD Gothic Neo"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Microsoft YaHei"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Microsoft YaHei"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -375,13 +946,255 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -394,18 +1207,65 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -615,34 +1475,34 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:P4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.13970588235294" defaultRowHeight="17.6" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="32" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.8529411764706" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.8529411764706" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.2867647058824" style="1" customWidth="1"/>
     <col min="5" max="5" width="11" style="1" customWidth="1"/>
     <col min="6" max="6" width="10" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.42578125" style="1" customWidth="1"/>
-    <col min="8" max="9" width="9.140625" style="1"/>
-    <col min="10" max="10" width="27.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.4264705882353" style="1" customWidth="1"/>
+    <col min="8" max="9" width="9.13970588235294" style="1"/>
+    <col min="10" max="10" width="27.7132352941176" style="1" customWidth="1"/>
     <col min="11" max="11" width="10" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" style="1"/>
+    <col min="12" max="12" width="9.13970588235294" style="1"/>
     <col min="13" max="13" width="62" style="1" customWidth="1"/>
-    <col min="14" max="14" width="10.85546875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="16.85546875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="14" max="14" width="10.8529411764706" style="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5735294117647" style="1" customWidth="1"/>
+    <col min="16" max="16" width="16.8529411764706" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.13970588235294" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="30" customHeight="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -689,24 +1549,24 @@
         <v>14</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="153" x14ac:dyDescent="0.2">
+    <row r="2" ht="141" spans="1:16">
       <c r="A2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="1" t="s">
         <v>16</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>17</v>
+      <c r="D2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="G2" s="1">
         <v>9999</v>
@@ -717,12 +1577,8 @@
       <c r="J2" s="1">
         <v>1</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="K2" s="4"/>
+      <c r="L2" s="1"/>
       <c r="M2" s="1">
         <v>12345</v>
       </c>
@@ -733,11 +1589,11 @@
         <v>0</v>
       </c>
       <c r="P2" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" ht="17.25" customHeight="1"/>
+    <row r="4" spans="1:11">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="D4" s="3"/>
@@ -745,8 +1601,8 @@
       <c r="K4" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/admin/public/imports/product/zh.xlsx
+++ b/admin/public/imports/product/zh.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="23960"/>
+    <workbookView windowWidth="3264" windowHeight="23960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>*商品名称</t>
   </si>
@@ -142,17 +142,50 @@
     <t>*堂食税类</t>
   </si>
   <si>
-    <t>*外带税类</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>外带税类</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">*计价方式
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（按整数计价=1，按小数计价=2）</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">*显示
 </t>
     </r>
@@ -164,7 +197,8 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>（可多选，是否显示到：收银机=1/平板=2/厨显=3/点餐助手=4/扫码点餐=5）</t>
+      <t>（可多选，是否显示到：收银机=1/平板=2/厨显=3/点餐助手=4/扫码点餐=5/外送=6）
+（注意：当计价方式=2时，只能显示到：收银机1/厨显3）</t>
     </r>
   </si>
   <si>
@@ -282,234 +316,24 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">English:Caramel pudding
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <charset val="134"/>
-      </rPr>
-      <t>ภาษาไทย</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <charset val="134"/>
-      </rPr>
-      <t>พุดดิ้งคาราเมล</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>简体中文</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>焦糖布丁</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>繁體中文</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>焦糖布丁</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
+    <t>（例，导入时请删除此行）
+English:Caramel pudding
+ภาษาไทย:พุดดิ้งคาราเมล
+简体中文:焦糖布丁
+繁體中文:焦糖布丁
 Türkçe:crème brûlée
 မြန်မာဘာသာ:ရွှင်ဆူမန်
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>日本語</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="冬青黑体简体中文"/>
-        <charset val="134"/>
-      </rPr>
-      <t>クレームブリュレ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Apple SD Gothic Neo"/>
-        <charset val="134"/>
-      </rPr>
-      <t>한국어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Apple SD Gothic Neo"/>
-        <charset val="134"/>
-      </rPr>
-      <t>크림</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Apple SD Gothic Neo"/>
-        <charset val="134"/>
-      </rPr>
-      <t>브륄레</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>甜点</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>非常甜</t>
-    </r>
+日本語:クレームブリュレ
+한국어:크림 브륄레</t>
+  </si>
+  <si>
+    <t>甜品/港式甜品</t>
   </si>
   <si>
     <t>份</t>
   </si>
   <si>
-    <t>小</t>
+    <t>酒水类</t>
   </si>
 </sst>
 </file>
@@ -522,7 +346,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="27">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -537,12 +361,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体-简"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -692,38 +510,6 @@
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="冬青黑体简体中文"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Apple SD Gothic Neo"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -741,6 +527,19 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体-简"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1049,148 +848,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1204,11 +1003,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1481,7 +1280,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr defaultColWidth="9.13970588235294" defaultRowHeight="17.6" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="32" style="1" customWidth="1"/>
@@ -1495,14 +1294,15 @@
     <col min="10" max="10" width="27.7132352941176" style="1" customWidth="1"/>
     <col min="11" max="11" width="10" style="1" customWidth="1"/>
     <col min="12" max="12" width="9.13970588235294" style="1"/>
-    <col min="13" max="13" width="62" style="1" customWidth="1"/>
-    <col min="14" max="14" width="10.8529411764706" style="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5735294117647" style="1" customWidth="1"/>
-    <col min="16" max="16" width="16.8529411764706" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.13970588235294" style="1"/>
+    <col min="13" max="13" width="29.7794117647059" style="1" customWidth="1"/>
+    <col min="14" max="14" width="62" style="1" customWidth="1"/>
+    <col min="15" max="15" width="10.8529411764706" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5735294117647" style="1" customWidth="1"/>
+    <col min="17" max="17" width="16.8529411764706" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.13970588235294" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:16">
+    <row r="1" ht="53" customHeight="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1545,27 +1345,30 @@
       <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" ht="141" spans="1:16">
+    <row r="2" ht="159" spans="1:17">
       <c r="A2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="4" t="s">
         <v>17</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="4" t="s">
+      <c r="D2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G2" s="1">
@@ -1577,28 +1380,35 @@
       <c r="J2" s="1">
         <v>1</v>
       </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="1"/>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="M2" s="1">
-        <v>12345</v>
+        <v>1</v>
       </c>
       <c r="N2" s="1">
-        <v>0</v>
+        <v>123456</v>
       </c>
       <c r="O2" s="1">
         <v>0</v>
       </c>
       <c r="P2" s="1">
         <v>0</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1"/>
     <row r="4" spans="1:11">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="K4" s="3"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="K4" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>

--- a/admin/public/imports/product/zh.xlsx
+++ b/admin/public/imports/product/zh.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="3264" windowHeight="23960"/>
+    <workbookView windowHeight="21780"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>*商品名称</t>
   </si>
@@ -186,6 +186,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">*显示
 </t>
     </r>
@@ -197,7 +204,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>（可多选，是否显示到：收银机=1/平板=2/厨显=3/点餐助手=4/扫码点餐=5/外送=6）
+      <t>（可多选，是否显示到：收银机=1/平板=2/厨显=3/点餐助手=4/扫码点餐=5/外卖=6）
 （注意：当计价方式=2时，只能显示到：收银机1/厨显3）</t>
     </r>
   </si>
@@ -229,13 +236,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -310,6 +310,75 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>整单折扣</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（开启</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=1/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>关闭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
         <charset val="134"/>
       </rPr>
       <t>）</t>
@@ -346,7 +415,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="29">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -512,6 +581,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体-简"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体-简"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Microsoft YaHei"/>
@@ -527,19 +621,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体-简"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -993,7 +1074,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1007,6 +1088,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1280,7 +1364,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultColWidth="9.13970588235294" defaultRowHeight="17.6" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="32" style="1" customWidth="1"/>
@@ -1299,10 +1383,11 @@
     <col min="15" max="15" width="10.8529411764706" style="1" customWidth="1"/>
     <col min="16" max="16" width="14.5735294117647" style="1" customWidth="1"/>
     <col min="17" max="17" width="16.8529411764706" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.13970588235294" style="1"/>
+    <col min="18" max="18" width="16.5367647058824" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.13970588235294" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="53" customHeight="1" spans="1:17">
+    <row r="1" ht="53" customHeight="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1351,25 +1436,28 @@
       <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="5" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" ht="159" spans="1:17">
+    <row r="2" ht="159" spans="1:18">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" s="1">
         <v>9999</v>
@@ -1381,10 +1469,10 @@
         <v>1</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M2" s="1">
         <v>1</v>
@@ -1399,6 +1487,9 @@
         <v>0</v>
       </c>
       <c r="Q2" s="1">
+        <v>1</v>
+      </c>
+      <c r="R2" s="1">
         <v>1</v>
       </c>
     </row>

--- a/admin/public/imports/product/zh.xlsx
+++ b/admin/public/imports/product/zh.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="21780"/>
+    <workbookView windowWidth="3264" windowHeight="21940"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -236,6 +236,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -317,6 +324,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -385,15 +398,235 @@
     </r>
   </si>
   <si>
-    <t>（例，导入时请删除此行）
+    <r>
+      <t>（例，导入时请删除此行）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
 English:Caramel pudding
-ภาษาไทย:พุดดิ้งคาราเมล
-简体中文:焦糖布丁
-繁體中文:焦糖布丁
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ภาษาไทย</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <charset val="134"/>
+      </rPr>
+      <t>พุดดิ้งคาราเมล</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>简体中文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>焦糖布丁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>繁體中文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>焦糖布丁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
 Türkçe:crème brûlée
 မြန်မာဘာသာ:ရွှင်ဆူမန်
-日本語:クレームブリュレ
-한국어:크림 브륄레</t>
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>日本語</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="冬青黑体简体中文"/>
+        <charset val="134"/>
+      </rPr>
+      <t>クレームブリュレ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Apple SD Gothic Neo"/>
+        <charset val="134"/>
+      </rPr>
+      <t>한국어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Apple SD Gothic Neo"/>
+        <charset val="134"/>
+      </rPr>
+      <t>크림</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Apple SD Gothic Neo"/>
+        <charset val="134"/>
+      </rPr>
+      <t>브륄레</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Svenska:Karamellpudding</t>
+    </r>
   </si>
   <si>
     <t>甜品/港式甜品</t>
@@ -415,7 +648,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="33">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -430,170 +663,213 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体-简"/>
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="冬青黑体简体中文"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Apple SD Gothic Neo"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体-简"/>
@@ -603,24 +879,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Microsoft YaHei"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Microsoft YaHei"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -929,148 +1187,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1087,10 +1345,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1430,7 +1688,7 @@
       <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="2" t="s">
@@ -1439,12 +1697,12 @@
       <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" ht="159" spans="1:18">
-      <c r="A2" s="2" t="s">
+    <row r="2" ht="176" spans="1:18">
+      <c r="A2" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -1495,11 +1753,11 @@
     </row>
     <row r="3" ht="17.25" customHeight="1"/>
     <row r="4" spans="1:11">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="K4" s="4"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="K4" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>

--- a/admin/public/imports/product/zh.xlsx
+++ b/admin/public/imports/product/zh.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="3264" windowHeight="21940"/>
+    <workbookView windowHeight="23860"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,236 +27,60 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
-  <si>
-    <t>*商品名称</t>
-  </si>
-  <si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+  <si>
+    <t>*名称</t>
+  </si>
+  <si>
+    <t>*分类
+（二级分类请以/分隔）</t>
+  </si>
+  <si>
+    <t>*单位</t>
+  </si>
+  <si>
+    <t>*规格</t>
+  </si>
+  <si>
+    <t>*价格</t>
+  </si>
+  <si>
+    <t>*计价方式
+（整数计价=1/小数计价=2）</t>
+  </si>
+  <si>
+    <t>条码</t>
+  </si>
+  <si>
+    <t>*上架
+（开启=0/关闭=1）</t>
+  </si>
+  <si>
+    <t>*堂食税类</t>
+  </si>
+  <si>
+    <t>*外带税类</t>
+  </si>
+  <si>
+    <t>*库存扣减
+（下单扣减=1/付款扣减=2）</t>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
     <r>
       <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">*所属分类
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（二级分类请以/分隔）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">*库存计算方式
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（下单减库存=1/付款减库存=2）</t>
-    </r>
-  </si>
-  <si>
-    <t>*商品单位</t>
-  </si>
-  <si>
-    <t>*规格名称</t>
-  </si>
-  <si>
-    <t>图片名称</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">*库存数量
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（最大库存：99999999）</t>
-    </r>
-  </si>
-  <si>
-    <t>商品条码</t>
-  </si>
-  <si>
-    <t>*商品价格</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">*商品状态
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（上架=1/下架=0）</t>
-    </r>
-  </si>
-  <si>
-    <t>*堂食税类</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>外带税类</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">*计价方式
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（按整数计价=1，按小数计价=2）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">*显示
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（可多选，是否显示到：收银机=1/平板=2/厨显=3/点餐助手=4/扫码点餐=5/外卖=6）
-（注意：当计价方式=2时，只能显示到：收银机1/厨显3）</t>
-    </r>
-  </si>
-  <si>
-    <t>商品排序</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">限购数量
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（0为不限购）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
+        <sz val="9"/>
         <color theme="1"/>
         <rFont val="Microsoft YaHei"/>
         <charset val="134"/>
       </rPr>
-      <t>会员折扣</t>
+      <t>显示</t>
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="9"/>
         <color theme="1"/>
         <rFont val="Arial"/>
         <charset val="134"/>
@@ -267,54 +91,121 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="9"/>
         <color theme="1"/>
         <rFont val="Microsoft YaHei"/>
         <charset val="134"/>
       </rPr>
-      <t>（开启</t>
+      <t>（可多选，是否显示到：收银机</t>
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>=1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
+        <sz val="9"/>
         <color theme="1"/>
         <rFont val="Arial"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>/</t>
+      <t>=1/</t>
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="9"/>
         <color theme="1"/>
         <rFont val="Microsoft YaHei"/>
         <charset val="134"/>
       </rPr>
-      <t>关闭</t>
+      <t>平板</t>
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="9"/>
         <color theme="1"/>
         <rFont val="Arial"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>=0</t>
+      <t>=2/</t>
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>厨显</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=3/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点餐助手</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=4/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>桌码点餐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=5/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>扫码点餐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
         <color theme="1"/>
         <rFont val="Microsoft YaHei"/>
         <charset val="134"/>
@@ -323,316 +214,34 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>整单折扣</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（开启</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>=1/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>关闭</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>=0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>（例，导入时请删除此行）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
+    <t>*会员折扣
+（开启=0/关闭=1）</t>
+  </si>
+  <si>
+    <t>*整单折扣
+（开启=0/关闭=1）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（例，导入时请删除此行）
 English:Caramel pudding
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <charset val="134"/>
-      </rPr>
-      <t>ภาษาไทย</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <charset val="134"/>
-      </rPr>
-      <t>พุดดิ้งคาราเมล</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>简体中文</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>焦糖布丁</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>繁體中文</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>焦糖布丁</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
+ภาษาไทย:พุดดิ้งคาราเมล
+简体中文:焦糖布丁
+繁體中文:焦糖布丁
 Türkçe:crème brûlée
 မြန်မာဘာသာ:ရွှင်ဆူမန်
+日本語:クレームブリュレ
+한국어:크림 브륄레
+Svenska:Karamellpudding
 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>日本語</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="冬青黑体简体中文"/>
-        <charset val="134"/>
-      </rPr>
-      <t>クレームブリュレ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Apple SD Gothic Neo"/>
-        <charset val="134"/>
-      </rPr>
-      <t>한국어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Apple SD Gothic Neo"/>
-        <charset val="134"/>
-      </rPr>
-      <t>크림</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Apple SD Gothic Neo"/>
-        <charset val="134"/>
-      </rPr>
-      <t>브륄레</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Svenska:Karamellpudding</t>
-    </r>
   </si>
   <si>
     <t>甜品/港式甜品</t>
   </si>
   <si>
     <t>份</t>
+  </si>
+  <si>
+    <t>标准</t>
   </si>
   <si>
     <t>酒水类</t>
@@ -648,13 +257,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="25">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -663,10 +278,11 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="9"/>
       <color theme="1"/>
-      <name val="宋体-简"/>
+      <name val="Arial"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -820,65 +436,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Microsoft YaHei"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Microsoft YaHei"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="冬青黑体简体中文"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Apple SD Gothic Neo"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体-简"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1187,148 +747,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1339,17 +899,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1622,37 +1182,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R4"/>
-  <sheetFormatPr defaultColWidth="9.13970588235294" defaultRowHeight="17.6" outlineLevelRow="3"/>
+  <dimension ref="A1:N23"/>
+  <sheetFormatPr defaultColWidth="9.13970588235294" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="32" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.8529411764706" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.8529411764706" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.2867647058824" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.4264705882353" style="1" customWidth="1"/>
-    <col min="8" max="9" width="9.13970588235294" style="1"/>
-    <col min="10" max="10" width="27.7132352941176" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.13970588235294" style="1"/>
-    <col min="13" max="13" width="29.7794117647059" style="1" customWidth="1"/>
-    <col min="14" max="14" width="62" style="1" customWidth="1"/>
-    <col min="15" max="15" width="10.8529411764706" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5735294117647" style="1" customWidth="1"/>
-    <col min="17" max="17" width="16.8529411764706" style="1" customWidth="1"/>
-    <col min="18" max="18" width="16.5367647058824" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.13970588235294" style="1"/>
+    <col min="1" max="1" width="29.5735294117647" style="2" customWidth="1"/>
+    <col min="2" max="2" width="18.8529411764706" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.5735294117647" customWidth="1"/>
+    <col min="4" max="4" width="14.8529411764706" customWidth="1"/>
+    <col min="5" max="5" width="12.1397058823529" customWidth="1"/>
+    <col min="6" max="6" width="21.8529411764706" customWidth="1"/>
+    <col min="7" max="7" width="10.2867647058824" customWidth="1"/>
+    <col min="8" max="8" width="14.7132352941176" customWidth="1"/>
+    <col min="9" max="9" width="10.7132352941176" style="2" customWidth="1"/>
+    <col min="10" max="10" width="12.5735294117647" customWidth="1"/>
+    <col min="11" max="11" width="21.7132352941176" style="2" customWidth="1"/>
+    <col min="12" max="12" width="62" style="2" customWidth="1"/>
+    <col min="13" max="13" width="17.4264705882353" customWidth="1"/>
+    <col min="14" max="14" width="15" style="2" customWidth="1"/>
+    <col min="15" max="15" width="14.5735294117647" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="9.13970588235294" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="53" customHeight="1" spans="1:18">
+    <row r="1" s="1" customFormat="1" ht="53.25" customHeight="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -1661,25 +1219,25 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="3" t="s">
@@ -1688,76 +1246,181 @@
       <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" ht="150" spans="1:14">
+      <c r="A2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" ht="176" spans="1:18">
-      <c r="A2" s="4" t="s">
+      <c r="E2" s="1">
+        <v>50</v>
+      </c>
+      <c r="F2" s="5">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="1">
+      <c r="J2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="1">
-        <v>9999</v>
-      </c>
-      <c r="I2" s="1">
-        <v>50</v>
-      </c>
-      <c r="J2" s="1">
-        <v>1</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>21</v>
+      <c r="L2" s="1">
+        <v>1234567</v>
       </c>
       <c r="M2" s="1">
         <v>1</v>
       </c>
       <c r="N2" s="1">
-        <v>123456</v>
-      </c>
-      <c r="O2" s="1">
-        <v>0</v>
-      </c>
-      <c r="P2" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="1">
         <v>1</v>
       </c>
-      <c r="R2" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" ht="17.25" customHeight="1"/>
-    <row r="4" spans="1:11">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="K4" s="5"/>
+    </row>
+    <row r="3" ht="17.25" customHeight="1" spans="14:14">
+      <c r="N3"/>
+    </row>
+    <row r="4" spans="3:14">
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="N4"/>
+    </row>
+    <row r="5" spans="3:13">
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="M5" s="2"/>
+    </row>
+    <row r="6" spans="3:13">
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="M6" s="2"/>
+    </row>
+    <row r="7" spans="14:14">
+      <c r="N7"/>
+    </row>
+    <row r="8" spans="3:13">
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="M8" s="2"/>
+    </row>
+    <row r="9" spans="3:13">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="M9" s="2"/>
+    </row>
+    <row r="10" spans="3:13">
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="M10" s="2"/>
+    </row>
+    <row r="11" spans="14:14">
+      <c r="N11"/>
+    </row>
+    <row r="12" spans="3:13">
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="M12" s="2"/>
+    </row>
+    <row r="13" spans="14:14">
+      <c r="N13"/>
+    </row>
+    <row r="14" spans="3:13">
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="M14" s="2"/>
+    </row>
+    <row r="15" spans="14:14">
+      <c r="N15"/>
+    </row>
+    <row r="16" spans="3:13">
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="M16" s="2"/>
+    </row>
+    <row r="17" spans="3:13">
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="M17" s="2"/>
+    </row>
+    <row r="18" spans="3:13">
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="M18" s="2"/>
+    </row>
+    <row r="19" spans="14:14">
+      <c r="N19"/>
+    </row>
+    <row r="20" spans="3:13">
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="M20" s="2"/>
+    </row>
+    <row r="21" spans="14:14">
+      <c r="N21"/>
+    </row>
+    <row r="22" spans="14:14">
+      <c r="N22"/>
+    </row>
+    <row r="23" spans="3:13">
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="M23" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>

--- a/admin/public/imports/product/zh.xlsx
+++ b/admin/public/imports/product/zh.xlsx
@@ -67,6 +67,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -1279,7 +1286,7 @@
         <v>1</v>
       </c>
       <c r="L2" s="1">
-        <v>1234567</v>
+        <v>123456</v>
       </c>
       <c r="M2" s="1">
         <v>1</v>

--- a/admin/public/imports/product/zh.xlsx
+++ b/admin/public/imports/product/zh.xlsx
@@ -27,67 +27,229 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
-  <si>
-    <t>*名称</t>
-  </si>
-  <si>
-    <t>*分类
-（二级分类请以/分隔）</t>
-  </si>
-  <si>
-    <t>*单位</t>
-  </si>
-  <si>
-    <t>*规格</t>
-  </si>
-  <si>
-    <t>*价格</t>
-  </si>
-  <si>
-    <t>*计价方式
-（整数计价=1/小数计价=2）</t>
-  </si>
-  <si>
-    <t>条码</t>
-  </si>
-  <si>
-    <t>*上架
-（开启=0/关闭=1）</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+  <si>
+    <t>*商品名称</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">*所属分类
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（二级分类请以/分隔）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">*库存计算方式
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（下单减库存=1/付款减库存=2）</t>
+    </r>
+  </si>
+  <si>
+    <t>*商品单位</t>
+  </si>
+  <si>
+    <t>*规格名称</t>
+  </si>
+  <si>
+    <t>图片名称</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">*库存数量
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（最大库存：99999999）</t>
+    </r>
+  </si>
+  <si>
+    <t>商品条码</t>
+  </si>
+  <si>
+    <t>*商品价格</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">*商品状态
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（上架=1/下架=0）</t>
+    </r>
   </si>
   <si>
     <t>*堂食税类</t>
   </si>
   <si>
-    <t>*外带税类</t>
-  </si>
-  <si>
-    <t>*库存扣减
-（下单扣减=1/付款扣减=2）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>外带税类</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
+      <t xml:space="preserve">*计价方式
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（按整数计价=1，按小数计价=2）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">*显示
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（可多选，是否显示到：收银机=1/平板=2/厨显=3/点餐助手=4/桌码点餐=5/扫码点餐=6）
+（注意：当计价方式=2时，只能显示到：收银机1/厨显3）</t>
+    </r>
+  </si>
+  <si>
+    <t>商品排序</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">限购数量
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（0为不限购）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
       <rPr>
-        <sz val="9"/>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="Microsoft YaHei"/>
         <charset val="134"/>
       </rPr>
-      <t>显示</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
+      <t>会员折扣</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
         <charset val="134"/>
@@ -98,157 +260,378 @@
     </r>
     <r>
       <rPr>
-        <sz val="9"/>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="Microsoft YaHei"/>
         <charset val="134"/>
       </rPr>
-      <t>（可多选，是否显示到：收银机</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
+      <t>（开启</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>关闭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>整单折扣</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（开启</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>=1/</t>
     </r>
     <r>
       <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <charset val="134"/>
-      </rPr>
-      <t>平板</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>=2/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <charset val="134"/>
-      </rPr>
-      <t>厨显</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>=3/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <charset val="134"/>
-      </rPr>
-      <t>点餐助手</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>=4/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <charset val="134"/>
-      </rPr>
-      <t>桌码点餐</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>=5/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <charset val="134"/>
-      </rPr>
-      <t>扫码点餐</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>=6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>关闭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
         <charset val="134"/>
       </rPr>
       <t>）</t>
     </r>
   </si>
   <si>
-    <t>*会员折扣
-（开启=0/关闭=1）</t>
-  </si>
-  <si>
-    <t>*整单折扣
-（开启=0/关闭=1）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（例，导入时请删除此行）
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（例，导入时请删除此行）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
 English:Caramel pudding
-ภาษาไทย:พุดดิ้งคาราเมล
-简体中文:焦糖布丁
-繁體中文:焦糖布丁
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ภาษาไทย</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <charset val="134"/>
+      </rPr>
+      <t>พุดดิ้งคาราเมล</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>简体中文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>焦糖布丁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>繁體中文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>焦糖布丁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
 Türkçe:crème brûlée
 မြန်မာဘာသာ:ရွှင်ဆူမန်
-日本語:クレームブリュレ
-한국어:크림 브륄레
-Svenska:Karamellpudding
 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>日本語</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="冬青黑体简体中文"/>
+        <charset val="134"/>
+      </rPr>
+      <t>クレームブリュレ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Apple SD Gothic Neo"/>
+        <charset val="134"/>
+      </rPr>
+      <t>한국어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Apple SD Gothic Neo"/>
+        <charset val="134"/>
+      </rPr>
+      <t>크림</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Apple SD Gothic Neo"/>
+        <charset val="134"/>
+      </rPr>
+      <t>브륄레</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Svenska:Karamellpudding</t>
+    </r>
   </si>
   <si>
     <t>甜品/港式甜品</t>
   </si>
   <si>
     <t>份</t>
-  </si>
-  <si>
-    <t>标准</t>
   </si>
   <si>
     <t>酒水类</t>
@@ -264,19 +647,13 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="33">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -285,11 +662,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="宋体-简"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -443,9 +819,65 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体-简"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="冬青黑体简体中文"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Apple SD Gothic Neo"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -754,148 +1186,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -906,17 +1338,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1189,35 +1621,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N23"/>
-  <sheetFormatPr defaultColWidth="9.13970588235294" defaultRowHeight="17.6"/>
+  <dimension ref="A1:R4"/>
+  <sheetFormatPr defaultColWidth="9.13970588235294" defaultRowHeight="17.6" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="1" width="29.5735294117647" style="2" customWidth="1"/>
-    <col min="2" max="2" width="18.8529411764706" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.5735294117647" customWidth="1"/>
-    <col min="4" max="4" width="14.8529411764706" customWidth="1"/>
-    <col min="5" max="5" width="12.1397058823529" customWidth="1"/>
-    <col min="6" max="6" width="21.8529411764706" customWidth="1"/>
-    <col min="7" max="7" width="10.2867647058824" customWidth="1"/>
-    <col min="8" max="8" width="14.7132352941176" customWidth="1"/>
-    <col min="9" max="9" width="10.7132352941176" style="2" customWidth="1"/>
-    <col min="10" max="10" width="12.5735294117647" customWidth="1"/>
-    <col min="11" max="11" width="21.7132352941176" style="2" customWidth="1"/>
-    <col min="12" max="12" width="62" style="2" customWidth="1"/>
-    <col min="13" max="13" width="17.4264705882353" customWidth="1"/>
-    <col min="14" max="14" width="15" style="2" customWidth="1"/>
-    <col min="15" max="15" width="14.5735294117647" style="2" customWidth="1"/>
-    <col min="16" max="16384" width="9.13970588235294" style="2"/>
+    <col min="1" max="1" width="32" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.8529411764706" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.8529411764706" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.2867647058824" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.4264705882353" style="1" customWidth="1"/>
+    <col min="8" max="9" width="9.13970588235294" style="1"/>
+    <col min="10" max="10" width="27.7132352941176" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.13970588235294" style="1"/>
+    <col min="13" max="13" width="29.7794117647059" style="1" customWidth="1"/>
+    <col min="14" max="14" width="62" style="1" customWidth="1"/>
+    <col min="15" max="15" width="10.8529411764706" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5735294117647" style="1" customWidth="1"/>
+    <col min="17" max="17" width="16.8529411764706" style="1" customWidth="1"/>
+    <col min="18" max="18" width="16.5367647058824" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.13970588235294" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="53.25" customHeight="1" spans="1:14">
+    <row r="1" ht="53" customHeight="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -1226,25 +1660,25 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="3" t="s">
@@ -1253,181 +1687,76 @@
       <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="150" spans="1:14">
+    <row r="2" ht="176" spans="1:18">
       <c r="A2" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="1">
+        <v>20</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="1">
+        <v>9999</v>
+      </c>
+      <c r="I2" s="1">
         <v>50</v>
       </c>
-      <c r="F2" s="5">
+      <c r="J2" s="1">
         <v>1</v>
       </c>
-      <c r="H2" s="1">
-        <v>0</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1</v>
-      </c>
-      <c r="L2" s="1">
-        <v>123456</v>
+      <c r="K2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="M2" s="1">
         <v>1</v>
       </c>
       <c r="N2" s="1">
+        <v>123456</v>
+      </c>
+      <c r="O2" s="1">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1">
         <v>1</v>
       </c>
+      <c r="R2" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" ht="17.25" customHeight="1" spans="14:14">
-      <c r="N3"/>
-    </row>
-    <row r="4" spans="3:14">
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="N4"/>
-    </row>
-    <row r="5" spans="3:13">
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="M5" s="2"/>
-    </row>
-    <row r="6" spans="3:13">
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="M6" s="2"/>
-    </row>
-    <row r="7" spans="14:14">
-      <c r="N7"/>
-    </row>
-    <row r="8" spans="3:13">
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="M8" s="2"/>
-    </row>
-    <row r="9" spans="3:13">
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="M9" s="2"/>
-    </row>
-    <row r="10" spans="3:13">
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="M10" s="2"/>
-    </row>
-    <row r="11" spans="14:14">
-      <c r="N11"/>
-    </row>
-    <row r="12" spans="3:13">
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="M12" s="2"/>
-    </row>
-    <row r="13" spans="14:14">
-      <c r="N13"/>
-    </row>
-    <row r="14" spans="3:13">
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="M14" s="2"/>
-    </row>
-    <row r="15" spans="14:14">
-      <c r="N15"/>
-    </row>
-    <row r="16" spans="3:13">
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="M16" s="2"/>
-    </row>
-    <row r="17" spans="3:13">
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="M17" s="2"/>
-    </row>
-    <row r="18" spans="3:13">
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="M18" s="2"/>
-    </row>
-    <row r="19" spans="14:14">
-      <c r="N19"/>
-    </row>
-    <row r="20" spans="3:13">
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="M20" s="2"/>
-    </row>
-    <row r="21" spans="14:14">
-      <c r="N21"/>
-    </row>
-    <row r="22" spans="14:14">
-      <c r="N22"/>
-    </row>
-    <row r="23" spans="3:13">
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="M23" s="2"/>
+    <row r="3" ht="17.25" customHeight="1"/>
+    <row r="4" spans="1:11">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="K4" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
